--- a/public/assets/templates/inspection.xlsx
+++ b/public/assets/templates/inspection.xlsx
@@ -978,7 +978,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="201">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1755,6 +1755,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
@@ -1865,9 +1869,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2298960</xdr:colOff>
+      <xdr:colOff>2298600</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>477720</xdr:rowOff>
+      <xdr:rowOff>477360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1881,7 +1885,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="891000" y="399240"/>
-          <a:ext cx="2008080" cy="852480"/>
+          <a:ext cx="2007720" cy="852120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -31369,88 +31373,88 @@
     </row>
     <row r="43" customFormat="false" ht="13.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C43" s="8"/>
-      <c r="D43" s="152"/>
-      <c r="E43" s="152"/>
-      <c r="F43" s="152"/>
-      <c r="G43" s="152"/>
-      <c r="H43" s="152"/>
-      <c r="I43" s="152"/>
-      <c r="J43" s="152"/>
-      <c r="K43" s="152"/>
-      <c r="L43" s="152"/>
-      <c r="M43" s="152"/>
-      <c r="N43" s="152"/>
-      <c r="O43" s="152"/>
-      <c r="P43" s="179"/>
-      <c r="Q43" s="179"/>
-      <c r="R43" s="179"/>
-      <c r="S43" s="179"/>
-      <c r="T43" s="179"/>
-      <c r="U43" s="179"/>
-      <c r="V43" s="179"/>
-      <c r="W43" s="179"/>
-      <c r="X43" s="179"/>
-      <c r="Y43" s="179"/>
-      <c r="Z43" s="179"/>
-      <c r="AA43" s="179"/>
+      <c r="D43" s="181" t="s">
+        <v>128</v>
+      </c>
+      <c r="E43" s="181"/>
+      <c r="F43" s="181"/>
+      <c r="G43" s="181"/>
+      <c r="H43" s="181"/>
+      <c r="I43" s="181"/>
+      <c r="J43" s="181"/>
+      <c r="K43" s="181"/>
+      <c r="L43" s="181"/>
+      <c r="M43" s="181"/>
+      <c r="N43" s="181"/>
+      <c r="O43" s="181"/>
+      <c r="P43" s="181"/>
+      <c r="Q43" s="181"/>
+      <c r="R43" s="181"/>
+      <c r="S43" s="181"/>
+      <c r="T43" s="181"/>
+      <c r="U43" s="181"/>
+      <c r="V43" s="181"/>
+      <c r="W43" s="181"/>
+      <c r="X43" s="181"/>
+      <c r="Y43" s="181"/>
+      <c r="Z43" s="181"/>
+      <c r="AA43" s="181"/>
       <c r="AB43" s="151"/>
     </row>
     <row r="44" customFormat="false" ht="13.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C44" s="8"/>
-      <c r="D44" s="152"/>
-      <c r="E44" s="152"/>
-      <c r="F44" s="152"/>
-      <c r="G44" s="152"/>
-      <c r="H44" s="152"/>
-      <c r="I44" s="152"/>
-      <c r="J44" s="152"/>
-      <c r="K44" s="152"/>
-      <c r="L44" s="152"/>
-      <c r="M44" s="152"/>
-      <c r="N44" s="152"/>
-      <c r="O44" s="152"/>
-      <c r="P44" s="179"/>
-      <c r="Q44" s="179"/>
-      <c r="R44" s="179"/>
-      <c r="S44" s="179"/>
-      <c r="T44" s="179"/>
-      <c r="U44" s="179"/>
-      <c r="V44" s="179"/>
-      <c r="W44" s="179"/>
-      <c r="X44" s="179"/>
-      <c r="Y44" s="179"/>
-      <c r="Z44" s="179"/>
-      <c r="AA44" s="179"/>
+      <c r="D44" s="182"/>
+      <c r="E44" s="182"/>
+      <c r="F44" s="182"/>
+      <c r="G44" s="182"/>
+      <c r="H44" s="182"/>
+      <c r="I44" s="182"/>
+      <c r="J44" s="182"/>
+      <c r="K44" s="182"/>
+      <c r="L44" s="182"/>
+      <c r="M44" s="182"/>
+      <c r="N44" s="182"/>
+      <c r="O44" s="182"/>
+      <c r="P44" s="182"/>
+      <c r="Q44" s="182"/>
+      <c r="R44" s="182"/>
+      <c r="S44" s="182"/>
+      <c r="T44" s="182"/>
+      <c r="U44" s="182"/>
+      <c r="V44" s="182"/>
+      <c r="W44" s="182"/>
+      <c r="X44" s="182"/>
+      <c r="Y44" s="182"/>
+      <c r="Z44" s="182"/>
+      <c r="AA44" s="182"/>
       <c r="AB44" s="151"/>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C45" s="8"/>
-      <c r="D45" s="181" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" s="181"/>
-      <c r="F45" s="181"/>
-      <c r="G45" s="181"/>
-      <c r="H45" s="181"/>
-      <c r="I45" s="181"/>
-      <c r="J45" s="181"/>
-      <c r="K45" s="181"/>
-      <c r="L45" s="181"/>
-      <c r="M45" s="181"/>
-      <c r="N45" s="181"/>
-      <c r="O45" s="181"/>
-      <c r="P45" s="181"/>
-      <c r="Q45" s="181"/>
-      <c r="R45" s="181"/>
-      <c r="S45" s="181"/>
-      <c r="T45" s="181"/>
-      <c r="U45" s="181"/>
-      <c r="V45" s="181"/>
-      <c r="W45" s="181"/>
-      <c r="X45" s="181"/>
-      <c r="Y45" s="181"/>
-      <c r="Z45" s="181"/>
-      <c r="AA45" s="181"/>
+      <c r="D45" s="182"/>
+      <c r="E45" s="182"/>
+      <c r="F45" s="182"/>
+      <c r="G45" s="182"/>
+      <c r="H45" s="182"/>
+      <c r="I45" s="182"/>
+      <c r="J45" s="182"/>
+      <c r="K45" s="182"/>
+      <c r="L45" s="182"/>
+      <c r="M45" s="182"/>
+      <c r="N45" s="182"/>
+      <c r="O45" s="182"/>
+      <c r="P45" s="182"/>
+      <c r="Q45" s="182"/>
+      <c r="R45" s="182"/>
+      <c r="S45" s="182"/>
+      <c r="T45" s="182"/>
+      <c r="U45" s="182"/>
+      <c r="V45" s="182"/>
+      <c r="W45" s="182"/>
+      <c r="X45" s="182"/>
+      <c r="Y45" s="182"/>
+      <c r="Z45" s="182"/>
+      <c r="AA45" s="182"/>
       <c r="AB45" s="151"/>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31782,19 +31786,19 @@
       <c r="L57" s="193"/>
       <c r="M57" s="190"/>
       <c r="N57" s="192"/>
-      <c r="O57" s="192"/>
-      <c r="P57" s="192"/>
-      <c r="Q57" s="192"/>
-      <c r="R57" s="192"/>
-      <c r="S57" s="192"/>
-      <c r="T57" s="192"/>
-      <c r="U57" s="192"/>
-      <c r="V57" s="192"/>
-      <c r="W57" s="192"/>
-      <c r="X57" s="192"/>
-      <c r="Y57" s="192"/>
-      <c r="Z57" s="192"/>
-      <c r="AA57" s="192"/>
+      <c r="O57" s="194"/>
+      <c r="P57" s="194"/>
+      <c r="Q57" s="194"/>
+      <c r="R57" s="194"/>
+      <c r="S57" s="194"/>
+      <c r="T57" s="194"/>
+      <c r="U57" s="194"/>
+      <c r="V57" s="194"/>
+      <c r="W57" s="194"/>
+      <c r="X57" s="194"/>
+      <c r="Y57" s="194"/>
+      <c r="Z57" s="194"/>
+      <c r="AA57" s="194"/>
       <c r="AB57" s="157"/>
     </row>
     <row r="58" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31810,19 +31814,19 @@
       <c r="L58" s="193"/>
       <c r="M58" s="190"/>
       <c r="N58" s="192"/>
-      <c r="O58" s="192"/>
-      <c r="P58" s="192"/>
-      <c r="Q58" s="192"/>
-      <c r="R58" s="192"/>
-      <c r="S58" s="192"/>
-      <c r="T58" s="192"/>
-      <c r="U58" s="192"/>
-      <c r="V58" s="192"/>
-      <c r="W58" s="192"/>
-      <c r="X58" s="192"/>
-      <c r="Y58" s="192"/>
-      <c r="Z58" s="192"/>
-      <c r="AA58" s="192"/>
+      <c r="O58" s="194"/>
+      <c r="P58" s="194"/>
+      <c r="Q58" s="194"/>
+      <c r="R58" s="194"/>
+      <c r="S58" s="194"/>
+      <c r="T58" s="194"/>
+      <c r="U58" s="194"/>
+      <c r="V58" s="194"/>
+      <c r="W58" s="194"/>
+      <c r="X58" s="194"/>
+      <c r="Y58" s="194"/>
+      <c r="Z58" s="194"/>
+      <c r="AA58" s="194"/>
       <c r="AB58" s="157"/>
     </row>
     <row r="59" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31838,76 +31842,76 @@
       <c r="L59" s="193"/>
       <c r="M59" s="27"/>
       <c r="N59" s="27"/>
-      <c r="O59" s="192"/>
-      <c r="P59" s="192"/>
-      <c r="Q59" s="192"/>
-      <c r="R59" s="192"/>
-      <c r="S59" s="192"/>
-      <c r="T59" s="192"/>
-      <c r="U59" s="192"/>
-      <c r="V59" s="192"/>
-      <c r="W59" s="192"/>
-      <c r="X59" s="192"/>
-      <c r="Y59" s="192"/>
-      <c r="Z59" s="192"/>
-      <c r="AA59" s="192"/>
-      <c r="AB59" s="194"/>
+      <c r="O59" s="194"/>
+      <c r="P59" s="194"/>
+      <c r="Q59" s="194"/>
+      <c r="R59" s="194"/>
+      <c r="S59" s="194"/>
+      <c r="T59" s="194"/>
+      <c r="U59" s="194"/>
+      <c r="V59" s="194"/>
+      <c r="W59" s="194"/>
+      <c r="X59" s="194"/>
+      <c r="Y59" s="194"/>
+      <c r="Z59" s="194"/>
+      <c r="AA59" s="194"/>
+      <c r="AB59" s="195"/>
     </row>
     <row r="60" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C60" s="8"/>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="195"/>
-      <c r="L60" s="195"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="196"/>
+      <c r="L60" s="196"/>
       <c r="M60" s="158"/>
-      <c r="N60" s="196"/>
-      <c r="O60" s="196"/>
-      <c r="P60" s="196"/>
-      <c r="Q60" s="196"/>
-      <c r="R60" s="196"/>
-      <c r="S60" s="196"/>
-      <c r="T60" s="196"/>
-      <c r="U60" s="196"/>
-      <c r="V60" s="196"/>
-      <c r="W60" s="196"/>
-      <c r="X60" s="196"/>
-      <c r="Y60" s="196"/>
-      <c r="Z60" s="196"/>
-      <c r="AA60" s="196"/>
-      <c r="AB60" s="194"/>
+      <c r="N60" s="197"/>
+      <c r="O60" s="197"/>
+      <c r="P60" s="197"/>
+      <c r="Q60" s="197"/>
+      <c r="R60" s="197"/>
+      <c r="S60" s="197"/>
+      <c r="T60" s="197"/>
+      <c r="U60" s="197"/>
+      <c r="V60" s="197"/>
+      <c r="W60" s="197"/>
+      <c r="X60" s="197"/>
+      <c r="Y60" s="197"/>
+      <c r="Z60" s="197"/>
+      <c r="AA60" s="197"/>
+      <c r="AB60" s="195"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C61" s="139"/>
-      <c r="D61" s="197"/>
-      <c r="E61" s="197"/>
-      <c r="F61" s="197"/>
-      <c r="G61" s="197"/>
-      <c r="H61" s="197"/>
-      <c r="I61" s="197"/>
-      <c r="J61" s="197"/>
-      <c r="K61" s="197"/>
-      <c r="L61" s="197"/>
-      <c r="M61" s="198"/>
-      <c r="N61" s="197"/>
-      <c r="O61" s="197"/>
-      <c r="P61" s="197"/>
-      <c r="Q61" s="197"/>
-      <c r="R61" s="197"/>
-      <c r="S61" s="197"/>
-      <c r="T61" s="197"/>
-      <c r="U61" s="197"/>
-      <c r="V61" s="197"/>
-      <c r="W61" s="197"/>
-      <c r="X61" s="197"/>
-      <c r="Y61" s="197"/>
-      <c r="Z61" s="197"/>
-      <c r="AA61" s="197"/>
-      <c r="AB61" s="199"/>
+      <c r="D61" s="198"/>
+      <c r="E61" s="198"/>
+      <c r="F61" s="198"/>
+      <c r="G61" s="198"/>
+      <c r="H61" s="198"/>
+      <c r="I61" s="198"/>
+      <c r="J61" s="198"/>
+      <c r="K61" s="198"/>
+      <c r="L61" s="198"/>
+      <c r="M61" s="199"/>
+      <c r="N61" s="198"/>
+      <c r="O61" s="198"/>
+      <c r="P61" s="198"/>
+      <c r="Q61" s="198"/>
+      <c r="R61" s="198"/>
+      <c r="S61" s="198"/>
+      <c r="T61" s="198"/>
+      <c r="U61" s="198"/>
+      <c r="V61" s="198"/>
+      <c r="W61" s="198"/>
+      <c r="X61" s="198"/>
+      <c r="Y61" s="198"/>
+      <c r="Z61" s="198"/>
+      <c r="AA61" s="198"/>
+      <c r="AB61" s="200"/>
     </row>
     <row r="62" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D62" s="145"/>
@@ -55578,8 +55582,8 @@
     <mergeCell ref="P35:T35"/>
     <mergeCell ref="P36:T36"/>
     <mergeCell ref="P37:T37"/>
-    <mergeCell ref="D45:AA45"/>
-    <mergeCell ref="D46:AA51"/>
+    <mergeCell ref="D43:AA43"/>
+    <mergeCell ref="D44:AA51"/>
     <mergeCell ref="D54:L54"/>
     <mergeCell ref="N54:AA54"/>
     <mergeCell ref="D55:L55"/>
